--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488266_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488266_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9159</v>
+        <v>5.8694</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5288</v>
+        <v>5.4084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3872</v>
+        <v>0.461</v>
       </c>
       <c r="G2" t="n">
         <v>1.4295</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>2.172</v>
+        <v>1.1254</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0854</v>
+        <v>0.965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1604</v>
       </c>
       <c r="V2" t="n">
         <v>2.2027</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6574</v>
+        <v>1.822</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1816</v>
+        <v>2.3079</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5242</v>
+        <v>-0.4859</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.9139</v>
+        <v>-1.2144</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2536</v>
+        <v>1.5367</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6603</v>
+        <v>-2.7511</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0613</v>
+        <v>1.8593</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5790999999999999</v>
+        <v>2.3142</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5178</v>
+        <v>-0.4549</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9752</v>
+        <v>-3.0737</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8327</v>
+        <v>-0.7775</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1426</v>
+        <v>-2.2961</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4823</v>
+        <v>2.9646</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.594</v>
+        <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2008</v>
+        <v>-0.5571</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3443</v>
+        <v>-0.1803</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1435</v>
+        <v>-0.3768</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8883</v>
+        <v>0.6289</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8877</v>
+        <v>0.6289</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>J. PONCE GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1971</v>
+        <v>1.3966</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0702</v>
+        <v>2.0113</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8731</v>
+        <v>-0.6147</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0335</v>
+        <v>0.9382</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1471</v>
+        <v>1.2593</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8863</v>
+        <v>-0.3211</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0841</v>
+        <v>3.432</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1858</v>
+        <v>1.503</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8983</v>
+        <v>1.929</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.0507</v>
+        <v>-2.4938</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0387</v>
+        <v>-0.2437</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.012</v>
+        <v>-2.2501</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.3352</v>
+        <v>0.3706</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.5586</v>
+        <v>-2.0382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1306</v>
+        <v>0.4023</v>
       </c>
       <c r="T4" t="n">
-        <v>0.342</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4726</v>
+        <v>-0.2151</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6294</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5733</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1596</v>
+        <v>0.9581</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8005</v>
+        <v>3.8311</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6409</v>
+        <v>-2.8731</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.256</v>
+        <v>4.0335</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5635</v>
+        <v>2.1471</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6925</v>
+        <v>1.8863</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2555</v>
+        <v>7.0841</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4214</v>
+        <v>3.1858</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1659</v>
+        <v>3.8983</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0005</v>
+        <v>-3.0507</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1421</v>
+        <v>-1.0387</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8584</v>
+        <v>-2.012</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>-3.3352</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-5.5586</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4892</v>
+        <v>-0.3696</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1467</v>
+        <v>0.1029</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6359</v>
+        <v>-0.4726</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2589</v>
+        <v>0.6294</v>
       </c>
       <c r="W5" t="n">
         <v>2.2027</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9439</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7622</v>
+        <v>0.9313</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4697</v>
+        <v>1.9972</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7075</v>
+        <v>-1.0659</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2144</v>
+        <v>-2.9139</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5367</v>
+        <v>-0.2536</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.7511</v>
+        <v>-2.6603</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8593</v>
+        <v>0.0613</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3142</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4549</v>
+        <v>-0.5178</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0737</v>
+        <v>-2.9752</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7775</v>
+        <v>-0.8327</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2961</v>
+        <v>-2.1426</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9646</v>
+        <v>1.4823</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9646</v>
+        <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6169</v>
+        <v>0.4747</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0184</v>
+        <v>1.1599</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5984</v>
+        <v>-0.6852</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6289</v>
+        <v>1.8883</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6289</v>
+        <v>1.8877</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. GARCÍA REYES</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3221</v>
+        <v>0.4954</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3221</v>
+        <v>1.7026</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1.2072</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3221</v>
+        <v>-2.256</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3221</v>
+        <v>-0.5635</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.6925</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3221</v>
+        <v>-0.2555</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>-0.4214</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1659</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-2.0005</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.1421</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.8584</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2446</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0696</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PONCE GONZALEZ</t>
+          <t>I. GARCÍA REYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2094</v>
+        <v>0.3221</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9226</v>
+        <v>0.3221</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7131999999999999</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9382</v>
+        <v>0.3221</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2593</v>
+        <v>0.3221</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3211</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.432</v>
+        <v>0.3221</v>
       </c>
       <c r="K10" t="n">
-        <v>1.503</v>
+        <v>0.3221</v>
       </c>
       <c r="L10" t="n">
-        <v>1.929</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4938</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2437</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2501</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7849</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4713</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3136</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.5653</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9929</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3291</v>
+        <v>0.4276</v>
       </c>
       <c r="G11" t="n">
         <v>0.3275</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4355</v>
+        <v>-0.337</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3261</v>
+        <v>-0.2276</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6608</v>
+        <v>-1.7522</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.225</v>
+        <v>-1.4641</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4358</v>
+        <v>-0.2881</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6586</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3683</v>
+        <v>0.277</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2699</v>
+        <v>0.0308</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0985</v>
+        <v>0.2462</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1962</v>
+        <v>-2.4801</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1489</v>
+        <v>-2.5066</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0473</v>
+        <v>0.0265</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2854</v>
@@ -1468,13 +1468,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3549</v>
+        <v>0.3613</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.143</v>
+        <v>0.4993</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.1611</v>
+        <v>-3.8115</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.8004</v>
+        <v>-4.6478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6393</v>
+        <v>0.8363</v>
       </c>
       <c r="G14" t="n">
         <v>-3.1544</v>
@@ -1546,13 +1546,13 @@
         <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1612</v>
+        <v>0.5108</v>
       </c>
       <c r="T14" t="n">
-        <v>0.291</v>
+        <v>0.4436</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1298</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.6451</v>
+        <v>-4.742</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.9071</v>
+        <v>-3.2008</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7381</v>
+        <v>-1.5411</v>
       </c>
       <c r="G15" t="n">
         <v>-1.965</v>
@@ -1624,13 +1624,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1423</v>
+        <v>-0.2391</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2363</v>
+        <v>-0.0575</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3785</v>
+        <v>-0.1816</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3144</v>
@@ -1657,16 +1657,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1591</v>
+        <v>-0.6120000000000028</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1654</v>
+        <v>5.712600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.3245</v>
+        <v>-6.3246</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.452699999999999</v>
+        <v>-7.4527</v>
       </c>
       <c r="H16" t="n">
         <v>4.105799999999999</v>
@@ -1702,16 +1702,16 @@
         <v>17.6023</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9264000000000007</v>
+        <v>1.4737</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6801</v>
+        <v>3.2271</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7535</v>
+        <v>-1.7536</v>
       </c>
       <c r="V16" t="n">
-        <v>6.2938</v>
+        <v>6.293799999999999</v>
       </c>
       <c r="W16" t="n">
         <v>10.0685</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>8.3317</v>
+        <v>9.8184</v>
       </c>
       <c r="E17" t="n">
-        <v>8.2166</v>
+        <v>9.1959</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1151</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>7.7443</v>
@@ -1780,13 +1780,13 @@
         <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6887</v>
+        <v>-0.2021</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2037</v>
+        <v>-0.2244</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.485</v>
+        <v>0.0224</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5181</v>
+        <v>3.4609</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6812</v>
+        <v>2.3874</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8369</v>
+        <v>1.0734</v>
       </c>
       <c r="G18" t="n">
         <v>2.7934</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0164</v>
+        <v>-0.0737</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.4859</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7961</v>
+        <v>-0.5596</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6441</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6441</v>
+        <v>3.27</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-2.4671</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6441</v>
+        <v>4.0866</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6441</v>
+        <v>1.8303</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2.2563</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6441</v>
+        <v>5.2117</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6441</v>
+        <v>2.4947</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.717</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.1251</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.6644</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.4607</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.1685</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1237</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0448</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.4476</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.3354</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.134</v>
+        <v>0.6441</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6824</v>
+        <v>0.6441</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5484</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4.0866</v>
+        <v>0.6441</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8303</v>
+        <v>0.6441</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2563</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2117</v>
+        <v>0.6441</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4947</v>
+        <v>0.6441</v>
       </c>
       <c r="L20" t="n">
-        <v>2.717</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1251</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6644</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4607</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8374</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7113</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1261</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4476</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.3354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4187</v>
+        <v>-0.8763</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1676</v>
+        <v>-1.6572</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7489</v>
+        <v>0.781</v>
       </c>
       <c r="G21" t="n">
         <v>0.3381</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3932</v>
+        <v>-0.0644</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.2689</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3654</v>
+        <v>-0.3333</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0765</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9946</v>
+        <v>-0.8913</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1879</v>
+        <v>-1.1346</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1825</v>
+        <v>0.2433</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4957</v>
+        <v>-1.4325</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2454</v>
+        <v>-1.0823</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2503</v>
+        <v>-0.3502</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8445</v>
+        <v>-1.2643</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1288</v>
+        <v>-0.6529</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7157</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3403</v>
+        <v>-0.1683</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3743</v>
+        <v>-0.4294</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.966</v>
+        <v>0.2611</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.24</v>
+        <v>0.1707</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6566</v>
+        <v>0.1296</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4166</v>
+        <v>0.041</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.145</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1341</v>
+        <v>0.2859</v>
       </c>
       <c r="F23" t="n">
-        <v>0.989</v>
+        <v>-1.1825</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6981000000000001</v>
+        <v>-1.4957</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0944</v>
+        <v>-0.2454</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7925</v>
+        <v>-1.2503</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7134</v>
+        <v>0.8445</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3923</v>
+        <v>0.1288</v>
       </c>
       <c r="L23" t="n">
-        <v>4.1057</v>
+        <v>0.7157</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0152</v>
+        <v>-2.3403</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.3743</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3131</v>
+        <v>-1.966</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9646</v>
+        <v>0.7411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.5586</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3102</v>
+        <v>-0.1421</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3967</v>
+        <v>-0.5586</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9135</v>
+        <v>0.4166</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2097</v>
+        <v>-1.6867</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4284</v>
+        <v>-2.1341</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2187</v>
+        <v>0.4474</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4325</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0823</v>
+        <v>-2.0944</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3502</v>
+        <v>2.7925</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2643</v>
+        <v>2.7134</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6529</v>
+        <v>-1.3923</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>4.1057</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1683</v>
+        <v>-2.0152</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4294</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2611</v>
+        <v>-1.3131</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3706</v>
+        <v>-2.9646</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-5.5586</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3706</v>
+        <v>2.594</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1477</v>
+        <v>0.7685</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1641</v>
+        <v>0.3967</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0164</v>
+        <v>0.3718</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.1888</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2248</v>
+        <v>-2.133</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0818</v>
+        <v>-2.8781</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3066</v>
+        <v>0.7452</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.0827</v>
+        <v>-0.9121</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6743</v>
+        <v>-3.6693</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4084</v>
+        <v>2.7572</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4065</v>
+        <v>-0.4398</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2406</v>
+        <v>-3.1355</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1659</v>
+        <v>2.6956</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.4892</v>
+        <v>-0.4723</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.915</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5743</v>
+        <v>0.0616</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9876</v>
+        <v>0.0031</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2137</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2261</v>
+        <v>-0.6355</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9444</v>
+        <v>0.6289</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.24</v>
+        <v>-2.8278</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6823</v>
+        <v>0.2005</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4422</v>
+        <v>-3.0283</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9121</v>
+        <v>-2.0827</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.6693</v>
+        <v>-0.6743</v>
       </c>
       <c r="I26" t="n">
-        <v>2.7572</v>
+        <v>-1.4084</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4398</v>
+        <v>1.4065</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.1355</v>
+        <v>1.2406</v>
       </c>
       <c r="L26" t="n">
-        <v>2.6956</v>
+        <v>0.1659</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4723</v>
+        <v>-3.4892</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-1.915</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0616</v>
+        <v>-1.5743</v>
       </c>
       <c r="P26" t="n">
+        <v>-0.1853</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-1.8529</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-3.7057</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.104</v>
+        <v>0.3846</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8344</v>
+        <v>0.3324</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9384</v>
+        <v>0.0522</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6289</v>
+        <v>-0.9444</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6289</v>
+        <v>0.3144</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.2359</v>
+        <v>-2.9496</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.7573</v>
+        <v>-1.8552</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4786</v>
+        <v>-1.0944</v>
       </c>
       <c r="G27" t="n">
         <v>-2.9288</v>
@@ -2560,13 +2560,13 @@
         <v>2.9646</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.2969</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5061</v>
+        <v>0.4082</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.0894</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-1.7621</v>
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.159199999999999</v>
+        <v>2.464900000000004</v>
       </c>
       <c r="E28" t="n">
-        <v>6.324299999999998</v>
+        <v>6.324599999999998</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.165299999999999</v>
+        <v>-3.859500000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>7.452800000000001</v>
+        <v>7.452799999999999</v>
       </c>
       <c r="H28" t="n">
         <v>-4.105699999999999</v>
@@ -2626,10 +2626,10 @@
         <v>-6.8762</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.0692</v>
+        <v>-4.069199999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9262999999999999</v>
+        <v>0.9262999999999997</v>
       </c>
       <c r="Q28" t="n">
         <v>-17.6021</v>
@@ -2638,13 +2638,13 @@
         <v>18.5288</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.9263999999999999</v>
+        <v>0.3791999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>1.7535</v>
+        <v>1.7536</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.68</v>
+        <v>-1.3743</v>
       </c>
       <c r="V28" t="n">
         <v>-6.2937</v>
